--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Alienazione beni mobili e immobili.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Alienazione beni mobili e immobili.xlsx
@@ -346,7 +346,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è aperta l'asta pubblica per la vendita di beni mobili e immobili comunali. 
+      <t xml:space="preserve"> è aperta l'asta pubblica per la vendita di beni mobili e immobili comunali.
 Hai tempo fino al </t>
     </r>
     <r>
@@ -402,7 +402,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
